--- a/projekt_analiza_posortowane_juz.xlsx
+++ b/projekt_analiza_posortowane_juz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zosia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDE1322-B663-4474-99F9-C94190F42349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B11BA3-6C5C-4B64-B407-BCF7D1D195C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pomiary wierszami" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="107">
   <si>
     <t>Seria</t>
   </si>
@@ -1112,13 +1112,22 @@
     <t>C [µF] (zmierzone)</t>
   </si>
   <si>
-    <t>Czas zmierzony [µs]</t>
-  </si>
-  <si>
     <t>Pomiary dla kondensatora 470 µF</t>
   </si>
   <si>
     <t>symetryczny czas ładowania i rozładowania</t>
+  </si>
+  <si>
+    <t>Średnie C [µF] (zmierzone)</t>
+  </si>
+  <si>
+    <t>Średni czas zmierzony [µs]</t>
+  </si>
+  <si>
+    <t>Odchylenie standard.  [µF]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> czas zmierzony [µs]</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1263,12 +1272,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1294,22 +1362,65 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -11933,7 +12044,7 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>505.69928571428574</v>
+        <v>505.69928571428602</v>
       </c>
       <c r="H5">
         <v>1.8142702041389418</v>
@@ -16060,7 +16171,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1996CEE3-8C50-4827-8B8B-8F0A9549D50B}">
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:X83"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.09765625" customWidth="1"/>
@@ -16069,1305 +16180,1578 @@
     <col min="5" max="5" width="11.09765625" customWidth="1"/>
     <col min="6" max="6" width="16.69921875" customWidth="1"/>
     <col min="7" max="7" width="19.796875" customWidth="1"/>
+    <col min="10" max="10" width="16.5" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="6.8984375" customWidth="1"/>
+    <col min="13" max="13" width="6.69921875" customWidth="1"/>
+    <col min="14" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="25.5" customWidth="1"/>
+    <col min="17" max="17" width="29.8984375" customWidth="1"/>
+    <col min="18" max="18" width="16.59765625" customWidth="1"/>
+    <col min="19" max="19" width="8.296875" customWidth="1"/>
+    <col min="20" max="20" width="6.296875" customWidth="1"/>
+    <col min="21" max="21" width="6.19921875" customWidth="1"/>
+    <col min="22" max="22" width="23.09765625" customWidth="1"/>
+    <col min="23" max="23" width="22.796875" customWidth="1"/>
+    <col min="24" max="24" width="23.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:24">
+      <c r="A1" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="J1" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="10" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="J2" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="N3" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="O3" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="P3" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4" s="19">
+        <v>470</v>
+      </c>
+      <c r="B4" s="19">
+        <v>220</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+      <c r="F4" s="16">
+        <v>515.5</v>
+      </c>
+      <c r="G4" s="15">
+        <v>249188</v>
+      </c>
+      <c r="J4" s="24">
+        <v>470</v>
+      </c>
+      <c r="K4" s="24">
+        <v>220</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="31">
+        <v>515.02714285714285</v>
+      </c>
+      <c r="O4" s="31">
+        <v>1.5079707637006263</v>
+      </c>
+      <c r="P4" s="31">
+        <v>248958.85714285713</v>
+      </c>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="11">
+        <v>2</v>
+      </c>
+      <c r="F5" s="17">
+        <v>515.29999999999995</v>
+      </c>
+      <c r="G5" s="13">
+        <v>249092</v>
+      </c>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5" s="32">
+        <v>505.69928571428602</v>
+      </c>
+      <c r="O5" s="31">
+        <v>1.8142702041389418</v>
+      </c>
+      <c r="P5" s="31">
+        <v>154230.85714285713</v>
+      </c>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="11">
+        <v>3</v>
+      </c>
+      <c r="F6" s="17">
+        <v>512.27</v>
+      </c>
+      <c r="G6" s="13">
+        <v>247628</v>
+      </c>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="N6" s="31">
+        <v>500.52714285714285</v>
+      </c>
+      <c r="O6" s="31">
+        <v>0.70324991259183978</v>
+      </c>
+      <c r="P6" s="31">
+        <v>93301.142857142855</v>
+      </c>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="11">
         <v>4</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="F7" s="17">
+        <v>514.26</v>
+      </c>
+      <c r="G7" s="13">
+        <v>248588</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="N7" s="31">
+        <v>489.78642857142859</v>
+      </c>
+      <c r="O7" s="31">
+        <v>3.1535806441441876</v>
+      </c>
+      <c r="P7" s="31">
+        <v>43690.285714285717</v>
+      </c>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="11">
+        <v>5</v>
+      </c>
+      <c r="F8" s="17">
+        <v>515.75</v>
+      </c>
+      <c r="G8" s="13">
+        <v>249308</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="31">
+        <v>502.59428571428572</v>
+      </c>
+      <c r="O8" s="31">
+        <v>2.0765863788947034</v>
+      </c>
+      <c r="P8" s="31">
+        <v>153283.71428571429</v>
+      </c>
+      <c r="R8" s="36"/>
+      <c r="S8" s="36"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="11">
+        <v>6</v>
+      </c>
+      <c r="F9" s="17">
+        <v>516</v>
+      </c>
+      <c r="G9" s="13">
+        <v>249428</v>
+      </c>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" s="31">
+        <v>473.14499999999998</v>
+      </c>
+      <c r="O9" s="31">
+        <v>0.42211463991523085</v>
+      </c>
+      <c r="P9" s="31">
+        <v>655918.85714285716</v>
+      </c>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="11">
+        <v>7</v>
+      </c>
+      <c r="F10" s="17">
+        <v>515.75</v>
+      </c>
+      <c r="G10" s="13">
+        <v>249308</v>
+      </c>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="N10" s="31">
+        <v>458.66142857142859</v>
+      </c>
+      <c r="O10" s="31">
+        <v>2.370192647616058</v>
+      </c>
+      <c r="P10" s="31">
+        <v>131948.57142857142</v>
+      </c>
+      <c r="R10" s="36"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="11">
+        <v>8</v>
+      </c>
+      <c r="F11" s="17">
+        <v>512.03</v>
+      </c>
+      <c r="G11" s="13">
+        <v>247508</v>
+      </c>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="N11" s="35">
+        <v>460.36357142857145</v>
+      </c>
+      <c r="O11" s="35">
+        <v>1.1252870207733094</v>
+      </c>
+      <c r="P11" s="35">
+        <v>186661.71428571429</v>
+      </c>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="11">
+        <v>9</v>
+      </c>
+      <c r="F12" s="17">
+        <v>516.01</v>
+      </c>
+      <c r="G12" s="13">
+        <v>249436</v>
+      </c>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="12">
+        <v>10</v>
+      </c>
+      <c r="F13" s="18">
+        <v>515.75</v>
+      </c>
+      <c r="G13" s="14">
+        <v>249308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="10">
         <v>1</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="F14" s="16">
+        <v>505.32</v>
+      </c>
+      <c r="G14" s="15">
+        <v>154116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="11">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="F15" s="17">
+        <v>499.79</v>
+      </c>
+      <c r="G15" s="13">
+        <v>152428</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="11">
+        <v>3</v>
+      </c>
+      <c r="F16" s="17">
+        <v>506.08</v>
+      </c>
+      <c r="G16" s="13">
+        <v>154348</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="11">
+        <v>4</v>
+      </c>
+      <c r="F17" s="17">
+        <v>505.72</v>
+      </c>
+      <c r="G17" s="13">
+        <v>154236</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="11">
         <v>5</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="9">
-        <v>470</v>
-      </c>
-      <c r="B4" s="9">
-        <v>220</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="F18" s="17">
+        <v>506.08</v>
+      </c>
+      <c r="G18" s="13">
+        <v>154348</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="11">
+        <v>6</v>
+      </c>
+      <c r="F19" s="17">
+        <v>505.3</v>
+      </c>
+      <c r="G19" s="13">
+        <v>154108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="11">
+        <v>7</v>
+      </c>
+      <c r="F20" s="17">
+        <v>506.11</v>
+      </c>
+      <c r="G20" s="13">
+        <v>154356</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="11">
+        <v>8</v>
+      </c>
+      <c r="F21" s="17">
+        <v>507.29</v>
+      </c>
+      <c r="G21" s="13">
+        <v>154716</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="11">
+        <v>9</v>
+      </c>
+      <c r="F22" s="17">
+        <v>505.3</v>
+      </c>
+      <c r="G22" s="13">
+        <v>154108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="12">
+        <v>10</v>
+      </c>
+      <c r="F23" s="18">
+        <v>506.5</v>
+      </c>
+      <c r="G23" s="14">
+        <v>154476</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="10">
+        <v>1</v>
+      </c>
+      <c r="F24" s="16">
+        <v>500.89</v>
+      </c>
+      <c r="G24" s="15">
+        <v>93368</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="11">
+        <v>2</v>
+      </c>
+      <c r="F25" s="17">
+        <v>500.24</v>
+      </c>
+      <c r="G25" s="13">
+        <v>93248</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="11">
+        <v>3</v>
+      </c>
+      <c r="F26" s="17">
+        <v>500.84</v>
+      </c>
+      <c r="G26" s="13">
+        <v>93360</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="11">
+        <v>4</v>
+      </c>
+      <c r="F27" s="17">
+        <v>500.2</v>
+      </c>
+      <c r="G27" s="13">
+        <v>93240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="11">
+        <v>5</v>
+      </c>
+      <c r="F28" s="17">
+        <v>498.91</v>
+      </c>
+      <c r="G28" s="13">
+        <v>93000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="11">
+        <v>6</v>
+      </c>
+      <c r="F29" s="17">
+        <v>500.84</v>
+      </c>
+      <c r="G29" s="13">
+        <v>93360</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="11">
+        <v>7</v>
+      </c>
+      <c r="F30" s="17">
+        <v>500.84</v>
+      </c>
+      <c r="G30" s="13">
+        <v>93360</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="11">
+        <v>8</v>
+      </c>
+      <c r="F31" s="17">
+        <v>500.84</v>
+      </c>
+      <c r="G31" s="13">
+        <v>93360</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="11">
+        <v>9</v>
+      </c>
+      <c r="F32" s="17">
+        <v>500.2</v>
+      </c>
+      <c r="G32" s="13">
+        <v>93240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="12">
+        <v>10</v>
+      </c>
+      <c r="F33" s="18">
+        <v>501.49</v>
+      </c>
+      <c r="G33" s="14">
+        <v>93480</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1</v>
+      </c>
+      <c r="F34" s="16">
+        <v>488.42</v>
+      </c>
+      <c r="G34" s="15">
+        <v>43568</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="11">
+        <v>2</v>
+      </c>
+      <c r="F35" s="17">
+        <v>489.76</v>
+      </c>
+      <c r="G35" s="13">
+        <v>43688</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="11">
+        <v>3</v>
+      </c>
+      <c r="F36" s="17">
+        <v>492.36</v>
+      </c>
+      <c r="G36" s="13">
+        <v>43920</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="11">
+        <v>4</v>
+      </c>
+      <c r="F37" s="17">
+        <v>496.49</v>
+      </c>
+      <c r="G37" s="13">
+        <v>44288</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="11">
+        <v>5</v>
+      </c>
+      <c r="F38" s="17">
+        <v>481.6</v>
+      </c>
+      <c r="G38" s="13">
+        <v>42960</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="11">
+        <v>6</v>
+      </c>
+      <c r="F39" s="17">
+        <v>489.67</v>
+      </c>
+      <c r="G39" s="13">
+        <v>43680</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="19"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="11">
+        <v>7</v>
+      </c>
+      <c r="F40" s="17">
+        <v>489.67</v>
+      </c>
+      <c r="G40" s="13">
+        <v>43680</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="11">
+        <v>8</v>
+      </c>
+      <c r="F41" s="17">
+        <v>489.67</v>
+      </c>
+      <c r="G41" s="13">
+        <v>43680</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="11">
+        <v>9</v>
+      </c>
+      <c r="F42" s="17">
+        <v>489.67</v>
+      </c>
+      <c r="G42" s="13">
+        <v>43680</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="12">
+        <v>10</v>
+      </c>
+      <c r="F43" s="18">
+        <v>489.67</v>
+      </c>
+      <c r="G43" s="14">
+        <v>43680</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="19">
+        <v>470</v>
+      </c>
+      <c r="B44" s="19">
+        <v>1000</v>
+      </c>
+      <c r="C44" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D44" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E44" s="10">
         <v>1</v>
       </c>
-      <c r="F4" s="18">
-        <v>515.5</v>
-      </c>
-      <c r="G4" s="17">
-        <v>249188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="13">
+      <c r="F44" s="16">
+        <v>503.66</v>
+      </c>
+      <c r="G44" s="15">
+        <v>153608</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="11">
         <v>2</v>
       </c>
-      <c r="F5" s="19">
-        <v>515.29999999999995</v>
-      </c>
-      <c r="G5" s="15">
-        <v>249092</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="13">
+      <c r="F45" s="17">
+        <v>498.52</v>
+      </c>
+      <c r="G45" s="13">
+        <v>152040</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="19"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="11">
         <v>3</v>
       </c>
-      <c r="F6" s="19">
-        <v>512.27</v>
-      </c>
-      <c r="G6" s="15">
-        <v>247628</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="13">
+      <c r="F46" s="17">
+        <v>502.45</v>
+      </c>
+      <c r="G46" s="13">
+        <v>153240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="11">
         <v>4</v>
       </c>
-      <c r="F7" s="19">
-        <v>514.26</v>
-      </c>
-      <c r="G7" s="15">
-        <v>248588</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="13">
+      <c r="F47" s="17">
+        <v>503.63</v>
+      </c>
+      <c r="G47" s="13">
+        <v>153600</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="11">
         <v>5</v>
       </c>
-      <c r="F8" s="19">
-        <v>515.75</v>
-      </c>
-      <c r="G8" s="15">
-        <v>249308</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="13">
+      <c r="F48" s="17">
+        <v>502.06</v>
+      </c>
+      <c r="G48" s="13">
+        <v>153120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="19"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="11">
         <v>6</v>
       </c>
-      <c r="F9" s="19">
-        <v>516</v>
-      </c>
-      <c r="G9" s="15">
-        <v>249428</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="13">
+      <c r="F49" s="17">
+        <v>505.22</v>
+      </c>
+      <c r="G49" s="13">
+        <v>154084</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="19"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="11">
         <v>7</v>
       </c>
-      <c r="F10" s="19">
-        <v>515.75</v>
-      </c>
-      <c r="G10" s="15">
-        <v>249308</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="13">
+      <c r="F50" s="17">
+        <v>499.3</v>
+      </c>
+      <c r="G50" s="13">
+        <v>152280</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="19"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="11">
         <v>8</v>
       </c>
-      <c r="F11" s="19">
-        <v>512.03</v>
-      </c>
-      <c r="G11" s="15">
-        <v>247508</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="13">
+      <c r="F51" s="17">
+        <v>504.42</v>
+      </c>
+      <c r="G51" s="13">
+        <v>153840</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="19"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="11">
         <v>9</v>
       </c>
-      <c r="F12" s="19">
-        <v>516.01</v>
-      </c>
-      <c r="G12" s="15">
-        <v>249436</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="14">
+      <c r="F52" s="17">
+        <v>501.66</v>
+      </c>
+      <c r="G52" s="13">
+        <v>153000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="19"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="12">
         <v>10</v>
       </c>
-      <c r="F13" s="20">
-        <v>515.75</v>
-      </c>
-      <c r="G13" s="16">
-        <v>249308</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9" t="s">
+      <c r="F53" s="18">
+        <v>503.63</v>
+      </c>
+      <c r="G53" s="14">
+        <v>153600</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="19"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D54" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E54" s="11">
         <v>1</v>
       </c>
-      <c r="F14" s="18">
-        <v>505.32</v>
-      </c>
-      <c r="G14" s="17">
-        <v>154116</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="13">
+      <c r="F54" s="17">
+        <v>473.25</v>
+      </c>
+      <c r="G54" s="13">
+        <v>656068</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="19"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="11">
         <v>2</v>
       </c>
-      <c r="F15" s="19">
-        <v>499.79</v>
-      </c>
-      <c r="G15" s="15">
-        <v>152428</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="13">
+      <c r="F55" s="17">
+        <v>473.77</v>
+      </c>
+      <c r="G55" s="13">
+        <v>656788</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="19"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="11">
         <v>3</v>
       </c>
-      <c r="F16" s="19">
-        <v>506.08</v>
-      </c>
-      <c r="G16" s="15">
-        <v>154348</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="13">
+      <c r="F56" s="17">
+        <v>473.34</v>
+      </c>
+      <c r="G56" s="13">
+        <v>656188</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="19"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="11">
         <v>4</v>
       </c>
-      <c r="F17" s="19">
-        <v>505.72</v>
-      </c>
-      <c r="G17" s="15">
-        <v>154236</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="13">
+      <c r="F57" s="17">
+        <v>472.31</v>
+      </c>
+      <c r="G57" s="13">
+        <v>654764</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="19"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="11">
         <v>5</v>
       </c>
-      <c r="F18" s="19">
-        <v>506.08</v>
-      </c>
-      <c r="G18" s="15">
-        <v>154348</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="13">
+      <c r="F58" s="17">
+        <v>473.41</v>
+      </c>
+      <c r="G58" s="13">
+        <v>656292</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="19"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="11">
         <v>6</v>
       </c>
-      <c r="F19" s="19">
-        <v>505.3</v>
-      </c>
-      <c r="G19" s="15">
-        <v>154108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="13">
+      <c r="F59" s="17">
+        <v>473.34</v>
+      </c>
+      <c r="G59" s="13">
+        <v>656188</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="19"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="11">
         <v>7</v>
       </c>
-      <c r="F20" s="19">
-        <v>506.11</v>
-      </c>
-      <c r="G20" s="15">
-        <v>154356</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="13">
+      <c r="F60" s="17">
+        <v>473.59</v>
+      </c>
+      <c r="G60" s="13">
+        <v>656532</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="19"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="11">
         <v>8</v>
       </c>
-      <c r="F21" s="19">
-        <v>507.29</v>
-      </c>
-      <c r="G21" s="15">
-        <v>154716</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="13">
+      <c r="F61" s="17">
+        <v>473</v>
+      </c>
+      <c r="G61" s="13">
+        <v>655716</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="19"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="11">
         <v>9</v>
       </c>
-      <c r="F22" s="19">
-        <v>505.3</v>
-      </c>
-      <c r="G22" s="15">
-        <v>154108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="14">
+      <c r="F62" s="17">
+        <v>472.38</v>
+      </c>
+      <c r="G62" s="13">
+        <v>654852</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="19"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="11">
         <v>10</v>
       </c>
-      <c r="F23" s="20">
-        <v>506.5</v>
-      </c>
-      <c r="G23" s="16">
-        <v>154476</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9" t="s">
+      <c r="F63" s="17">
+        <v>473.16</v>
+      </c>
+      <c r="G63" s="13">
+        <v>655940</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="19"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D64" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E64" s="10">
         <v>1</v>
       </c>
-      <c r="F24" s="18">
-        <v>500.89</v>
-      </c>
-      <c r="G24" s="17">
-        <v>93368</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="13">
+      <c r="F64" s="16">
+        <v>458.84</v>
+      </c>
+      <c r="G64" s="15">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="19"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="11">
         <v>2</v>
       </c>
-      <c r="F25" s="19">
-        <v>500.24</v>
-      </c>
-      <c r="G25" s="15">
-        <v>93248</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="13">
+      <c r="F65" s="17">
+        <v>458.42</v>
+      </c>
+      <c r="G65" s="13">
+        <v>131880</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="19"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="11">
         <v>3</v>
       </c>
-      <c r="F26" s="19">
-        <v>500.84</v>
-      </c>
-      <c r="G26" s="15">
-        <v>93360</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="13">
+      <c r="F66" s="17">
+        <v>458.84</v>
+      </c>
+      <c r="G66" s="13">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="19"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="11">
         <v>4</v>
       </c>
-      <c r="F27" s="19">
-        <v>500.2</v>
-      </c>
-      <c r="G27" s="15">
-        <v>93240</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="13">
+      <c r="F67" s="17">
+        <v>462.18</v>
+      </c>
+      <c r="G67" s="13">
+        <v>132960</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="19"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="11">
         <v>5</v>
       </c>
-      <c r="F28" s="19">
-        <v>498.91</v>
-      </c>
-      <c r="G28" s="15">
-        <v>93000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="13">
+      <c r="F68" s="17">
+        <v>458.42</v>
+      </c>
+      <c r="G68" s="13">
+        <v>131880</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="19"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="11">
         <v>6</v>
       </c>
-      <c r="F29" s="19">
-        <v>500.84</v>
-      </c>
-      <c r="G29" s="15">
-        <v>93360</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="13">
+      <c r="F69" s="17">
+        <v>457.59</v>
+      </c>
+      <c r="G69" s="13">
+        <v>131640</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="19"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="11">
         <v>7</v>
       </c>
-      <c r="F30" s="19">
-        <v>500.84</v>
-      </c>
-      <c r="G30" s="15">
-        <v>93360</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="13">
+      <c r="F70" s="17">
+        <v>457.59</v>
+      </c>
+      <c r="G70" s="13">
+        <v>131640</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="19"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="11">
         <v>8</v>
       </c>
-      <c r="F31" s="19">
-        <v>500.84</v>
-      </c>
-      <c r="G31" s="15">
-        <v>93360</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="13">
+      <c r="F71" s="17">
+        <v>456.34</v>
+      </c>
+      <c r="G71" s="13">
+        <v>131280</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="19"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="11">
         <v>9</v>
       </c>
-      <c r="F32" s="19">
-        <v>500.2</v>
-      </c>
-      <c r="G32" s="15">
-        <v>93240</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="14">
+      <c r="F72" s="17">
+        <v>462.18</v>
+      </c>
+      <c r="G72" s="13">
+        <v>132960</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="19"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="12">
         <v>10</v>
       </c>
-      <c r="F33" s="20">
-        <v>501.49</v>
-      </c>
-      <c r="G33" s="16">
-        <v>93480</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9" t="s">
+      <c r="F73" s="18">
+        <v>463.43</v>
+      </c>
+      <c r="G73" s="14">
+        <v>133320</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="19"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D74" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E74" s="11">
         <v>1</v>
       </c>
-      <c r="F34" s="18">
-        <v>488.42</v>
-      </c>
-      <c r="G34" s="17">
-        <v>43568</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="13">
+      <c r="F74" s="17">
+        <v>458.73</v>
+      </c>
+      <c r="G74" s="13">
+        <v>186000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="19"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="11">
         <v>2</v>
       </c>
-      <c r="F35" s="19">
-        <v>489.76</v>
-      </c>
-      <c r="G35" s="15">
-        <v>43688</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="13">
+      <c r="F75" s="17">
+        <v>460.53</v>
+      </c>
+      <c r="G75" s="13">
+        <v>186728</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="19"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="11">
         <v>3</v>
       </c>
-      <c r="F36" s="19">
-        <v>492.36</v>
-      </c>
-      <c r="G36" s="15">
-        <v>43920</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="13">
+      <c r="F76" s="17">
+        <v>460.21</v>
+      </c>
+      <c r="G76" s="13">
+        <v>186600</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="19"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="11">
         <v>4</v>
       </c>
-      <c r="F37" s="19">
-        <v>496.49</v>
-      </c>
-      <c r="G37" s="15">
-        <v>44288</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="13">
+      <c r="F77" s="17">
+        <v>460.21</v>
+      </c>
+      <c r="G77" s="13">
+        <v>186600</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="19"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="11">
         <v>5</v>
       </c>
-      <c r="F38" s="19">
-        <v>481.6</v>
-      </c>
-      <c r="G38" s="15">
-        <v>42960</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="13">
+      <c r="F78" s="17">
+        <v>460.21</v>
+      </c>
+      <c r="G78" s="13">
+        <v>186600</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="19"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="19"/>
+      <c r="E79" s="11">
         <v>6</v>
       </c>
-      <c r="F39" s="19">
-        <v>489.67</v>
-      </c>
-      <c r="G39" s="15">
-        <v>43680</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="13">
+      <c r="F79" s="17">
+        <v>460.21</v>
+      </c>
+      <c r="G79" s="13">
+        <v>186600</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="19"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="11">
         <v>7</v>
       </c>
-      <c r="F40" s="19">
-        <v>489.67</v>
-      </c>
-      <c r="G40" s="15">
-        <v>43680</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="13">
+      <c r="F80" s="17">
+        <v>460.23</v>
+      </c>
+      <c r="G80" s="13">
+        <v>186608</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="19"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="19"/>
+      <c r="E81" s="11">
         <v>8</v>
       </c>
-      <c r="F41" s="19">
-        <v>489.67</v>
-      </c>
-      <c r="G41" s="15">
-        <v>43680</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="13">
+      <c r="F81" s="17">
+        <v>459.32</v>
+      </c>
+      <c r="G81" s="13">
+        <v>186240</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="19"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="19"/>
+      <c r="E82" s="11">
         <v>9</v>
       </c>
-      <c r="F42" s="19">
-        <v>489.67</v>
-      </c>
-      <c r="G42" s="15">
-        <v>43680</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="14">
+      <c r="F82" s="17">
+        <v>460.82</v>
+      </c>
+      <c r="G82" s="13">
+        <v>186848</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="19"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="12">
         <v>10</v>
       </c>
-      <c r="F43" s="20">
-        <v>489.67</v>
-      </c>
-      <c r="G43" s="16">
-        <v>43680</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="9">
-        <v>470</v>
-      </c>
-      <c r="B44" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E44" s="12">
-        <v>1</v>
-      </c>
-      <c r="F44" s="18">
-        <v>503.66</v>
-      </c>
-      <c r="G44" s="17">
-        <v>153608</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="13">
-        <v>2</v>
-      </c>
-      <c r="F45" s="19">
-        <v>498.52</v>
-      </c>
-      <c r="G45" s="15">
-        <v>152040</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="13">
-        <v>3</v>
-      </c>
-      <c r="F46" s="19">
-        <v>502.45</v>
-      </c>
-      <c r="G46" s="15">
-        <v>153240</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="13">
-        <v>4</v>
-      </c>
-      <c r="F47" s="19">
-        <v>503.63</v>
-      </c>
-      <c r="G47" s="15">
-        <v>153600</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="13">
-        <v>5</v>
-      </c>
-      <c r="F48" s="19">
-        <v>502.06</v>
-      </c>
-      <c r="G48" s="15">
-        <v>153120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="13">
-        <v>6</v>
-      </c>
-      <c r="F49" s="19">
-        <v>505.22</v>
-      </c>
-      <c r="G49" s="15">
-        <v>154084</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="13">
-        <v>7</v>
-      </c>
-      <c r="F50" s="19">
-        <v>499.3</v>
-      </c>
-      <c r="G50" s="15">
-        <v>152280</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="13">
-        <v>8</v>
-      </c>
-      <c r="F51" s="19">
-        <v>504.42</v>
-      </c>
-      <c r="G51" s="15">
-        <v>153840</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="13">
-        <v>9</v>
-      </c>
-      <c r="F52" s="19">
-        <v>501.66</v>
-      </c>
-      <c r="G52" s="15">
-        <v>153000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="14">
-        <v>10</v>
-      </c>
-      <c r="F53" s="20">
-        <v>503.63</v>
-      </c>
-      <c r="G53" s="16">
-        <v>153600</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="13">
-        <v>1</v>
-      </c>
-      <c r="F54" s="19">
-        <v>473.25</v>
-      </c>
-      <c r="G54" s="15">
-        <v>656068</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="13">
-        <v>2</v>
-      </c>
-      <c r="F55" s="19">
-        <v>473.77</v>
-      </c>
-      <c r="G55" s="15">
-        <v>656788</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="13">
-        <v>3</v>
-      </c>
-      <c r="F56" s="19">
-        <v>473.34</v>
-      </c>
-      <c r="G56" s="15">
-        <v>656188</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="13">
-        <v>4</v>
-      </c>
-      <c r="F57" s="19">
-        <v>472.31</v>
-      </c>
-      <c r="G57" s="15">
-        <v>654764</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="13">
-        <v>5</v>
-      </c>
-      <c r="F58" s="19">
-        <v>473.41</v>
-      </c>
-      <c r="G58" s="15">
-        <v>656292</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="13">
-        <v>6</v>
-      </c>
-      <c r="F59" s="19">
-        <v>473.34</v>
-      </c>
-      <c r="G59" s="15">
-        <v>656188</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="13">
-        <v>7</v>
-      </c>
-      <c r="F60" s="19">
-        <v>473.59</v>
-      </c>
-      <c r="G60" s="15">
-        <v>656532</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="13">
-        <v>8</v>
-      </c>
-      <c r="F61" s="19">
-        <v>473</v>
-      </c>
-      <c r="G61" s="15">
-        <v>655716</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="13">
-        <v>9</v>
-      </c>
-      <c r="F62" s="19">
-        <v>472.38</v>
-      </c>
-      <c r="G62" s="15">
-        <v>654852</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="9"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="13">
-        <v>10</v>
-      </c>
-      <c r="F63" s="19">
-        <v>473.16</v>
-      </c>
-      <c r="G63" s="15">
-        <v>655940</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E64" s="12">
-        <v>1</v>
-      </c>
-      <c r="F64" s="18">
-        <v>458.84</v>
-      </c>
-      <c r="G64" s="17">
-        <v>132000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="13">
-        <v>2</v>
-      </c>
-      <c r="F65" s="19">
-        <v>458.42</v>
-      </c>
-      <c r="G65" s="15">
-        <v>131880</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="13">
-        <v>3</v>
-      </c>
-      <c r="F66" s="19">
-        <v>458.84</v>
-      </c>
-      <c r="G66" s="15">
-        <v>132000</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="13">
-        <v>4</v>
-      </c>
-      <c r="F67" s="19">
-        <v>462.18</v>
-      </c>
-      <c r="G67" s="15">
-        <v>132960</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="13">
-        <v>5</v>
-      </c>
-      <c r="F68" s="19">
-        <v>458.42</v>
-      </c>
-      <c r="G68" s="15">
-        <v>131880</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="9"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="13">
-        <v>6</v>
-      </c>
-      <c r="F69" s="19">
-        <v>457.59</v>
-      </c>
-      <c r="G69" s="15">
-        <v>131640</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="9"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="13">
-        <v>7</v>
-      </c>
-      <c r="F70" s="19">
-        <v>457.59</v>
-      </c>
-      <c r="G70" s="15">
-        <v>131640</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="9"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="13">
-        <v>8</v>
-      </c>
-      <c r="F71" s="19">
-        <v>456.34</v>
-      </c>
-      <c r="G71" s="15">
-        <v>131280</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="13">
-        <v>9</v>
-      </c>
-      <c r="F72" s="19">
-        <v>462.18</v>
-      </c>
-      <c r="G72" s="15">
-        <v>132960</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="14">
-        <v>10</v>
-      </c>
-      <c r="F73" s="20">
-        <v>463.43</v>
-      </c>
-      <c r="G73" s="16">
-        <v>133320</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E74" s="13">
-        <v>1</v>
-      </c>
-      <c r="F74" s="19">
-        <v>458.73</v>
-      </c>
-      <c r="G74" s="15">
-        <v>186000</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="9"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="13">
-        <v>2</v>
-      </c>
-      <c r="F75" s="19">
-        <v>460.53</v>
-      </c>
-      <c r="G75" s="15">
-        <v>186728</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="9"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="13">
-        <v>3</v>
-      </c>
-      <c r="F76" s="19">
+      <c r="F83" s="18">
         <v>460.21</v>
       </c>
-      <c r="G76" s="15">
+      <c r="G83" s="14">
         <v>186600</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="9"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="13">
-        <v>4</v>
-      </c>
-      <c r="F77" s="19">
-        <v>460.21</v>
-      </c>
-      <c r="G77" s="15">
-        <v>186600</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="9"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="13">
-        <v>5</v>
-      </c>
-      <c r="F78" s="19">
-        <v>460.21</v>
-      </c>
-      <c r="G78" s="15">
-        <v>186600</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="9"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="13">
-        <v>6</v>
-      </c>
-      <c r="F79" s="19">
-        <v>460.21</v>
-      </c>
-      <c r="G79" s="15">
-        <v>186600</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="13">
-        <v>7</v>
-      </c>
-      <c r="F80" s="19">
-        <v>460.23</v>
-      </c>
-      <c r="G80" s="15">
-        <v>186608</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="13">
-        <v>8</v>
-      </c>
-      <c r="F81" s="19">
-        <v>459.32</v>
-      </c>
-      <c r="G81" s="15">
-        <v>186240</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="13">
-        <v>9</v>
-      </c>
-      <c r="F82" s="19">
-        <v>460.82</v>
-      </c>
-      <c r="G82" s="15">
-        <v>186848</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="14">
-        <v>10</v>
-      </c>
-      <c r="F83" s="20">
-        <v>460.21</v>
-      </c>
-      <c r="G83" s="16">
-        <v>186600</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A44:A83"/>
-    <mergeCell ref="B44:B83"/>
-    <mergeCell ref="C44:C53"/>
-    <mergeCell ref="D44:D53"/>
-    <mergeCell ref="C54:C63"/>
-    <mergeCell ref="D54:D63"/>
-    <mergeCell ref="C64:C73"/>
-    <mergeCell ref="D64:D73"/>
-    <mergeCell ref="C74:C83"/>
-    <mergeCell ref="D74:D83"/>
+  <mergeCells count="27">
+    <mergeCell ref="K4:K7"/>
+    <mergeCell ref="J4:J11"/>
+    <mergeCell ref="K8:K11"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="J2:P2"/>
     <mergeCell ref="C24:C33"/>
     <mergeCell ref="D24:D33"/>
     <mergeCell ref="C34:C43"/>
@@ -17380,6 +17764,16 @@
     <mergeCell ref="D4:D13"/>
     <mergeCell ref="C14:C23"/>
     <mergeCell ref="D14:D23"/>
+    <mergeCell ref="A44:A83"/>
+    <mergeCell ref="B44:B83"/>
+    <mergeCell ref="C44:C53"/>
+    <mergeCell ref="D44:D53"/>
+    <mergeCell ref="C54:C63"/>
+    <mergeCell ref="D54:D63"/>
+    <mergeCell ref="C64:C73"/>
+    <mergeCell ref="D64:D73"/>
+    <mergeCell ref="C74:C83"/>
+    <mergeCell ref="D74:D83"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
